--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_atacama_evolucion.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_atacama_evolucion.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Acumulado_desde_2018" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Acumulado_desde_2018'!$A$1:$C$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Acumulado_desde_2018'!$A$1:$C$97</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -34,7 +34,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:08</t>
+    <t xml:space="preserve">2026-09-29 14:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -503,8 +503,48 @@
         <v>-2.15</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>-5.2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>-8.52</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>-2.4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>-3.21</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B2"/>
+  <autoFilter ref="A1:B7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -778,8 +818,888 @@
         <v>-29.35</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>-20.24</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>-10.54</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>-7.53</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>7.55</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>11.54</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>4.26</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>8.75</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>11.65</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>9.12</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>-7.32</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>8.37</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>-8.05</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>9.66</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>-7.28</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>8.76</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>-32.04</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>-25.89</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>-15.54</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>11.22</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>-1.19</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>5.82</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>13.81</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>11.52</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>-13.99</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>-3.17</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>19.31</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>-13.02</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>-19.06</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>-24.96</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>-35.25</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>-12.87</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>27.96</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>27.87</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>23.42</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>30.53</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>11.64</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>33.47</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>30.83</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>4.68</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>12.38</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>-27.93</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>40.42</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>-14.54</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>3.84</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>-31.35</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>-45.53</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>-15.33</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>33.73</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>33.12</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>28.99</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>41.36</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>13.47</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>42.28</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>39.37</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>8.67</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>13.88</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B78" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>-35.9</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B79" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>51.81</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B80" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>-24.26</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B81" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>15.53</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B82" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>-37.23</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B83" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>-55.93</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B84" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>-18.92</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B85" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>40.34</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B86" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>36.9</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B87" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>32.72</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B88" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>48.57</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B89" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>15.42</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B90" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v>50.04</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B91" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>46.58</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B92" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v>10.16</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B93" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v>13.98</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B94" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>-42.31</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B95" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>60.08</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B96" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>-29.53</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B97" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v>26.54</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C17"/>
+  <autoFilter ref="A1:C97"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_atacama_evolucion.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_atacama_evolucion.xlsx
@@ -34,7 +34,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:02</t>
+    <t xml:space="preserve">2026-09-29 18:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_atacama_evolucion.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_atacama_evolucion.xlsx
@@ -34,7 +34,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:35</t>
+    <t xml:space="preserve">2026-10-05 04:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
